--- a/report_forms/046_crowdstrike_incident_response_form--report_forms.xlsx
+++ b/report_forms/046_crowdstrike_incident_response_form--report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -765,8 +765,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -794,12 +794,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'phishing_attack',_'value':_'phishing'}</t>
+          <t>phishing_attack</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Phishing Attack', 'value': 'Phishing'}</t>
+          <t>Phishing Attack</t>
         </is>
       </c>
     </row>
@@ -811,12 +811,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'malware_attack',_'value':_'malware'}</t>
+          <t>malware_attack</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Malware Attack', 'value': 'Malware'}</t>
+          <t>Malware Attack</t>
         </is>
       </c>
     </row>
@@ -828,12 +828,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'denial_of_service',_'value':_'denial_of_service'}</t>
+          <t>denial_of_service</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Denial of Service', 'value': 'Denial of Service'}</t>
+          <t>Denial of Service</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'ransomware',_'value':_'ransomware'}</t>
+          <t>ransomware</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Ransomware', 'value': 'Ransomware'}</t>
+          <t>Ransomware</t>
         </is>
       </c>
     </row>
@@ -862,12 +862,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'remote',_'value':_'remote'}</t>
+          <t>remote</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Remote', 'value': 'Remote'}</t>
+          <t>Remote</t>
         </is>
       </c>
     </row>
@@ -879,12 +879,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'local',_'value':_'local'}</t>
+          <t>local</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Local', 'value': 'Local'}</t>
+          <t>Local</t>
         </is>
       </c>
     </row>
@@ -896,12 +896,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'low',_'value':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Low', 'value': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -913,12 +913,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'medium',_'value':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Medium', 'value': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -930,12 +930,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'high',_'value':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'High', 'value': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -947,12 +947,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'resolved',_'value':_'resolved'}</t>
+          <t>resolved</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Resolved', 'value': 'Resolved'}</t>
+          <t>Resolved</t>
         </is>
       </c>
     </row>
@@ -964,12 +964,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'in_progress',_'value':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'In Progress', 'value': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -981,12 +981,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'pending',_'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Pending', 'value': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
